--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487598_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487598_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.325</v>
+        <v>3.6759</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2917</v>
+        <v>1.7517</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0333</v>
+        <v>1.9242</v>
       </c>
       <c r="G2" t="n">
         <v>0.2458</v>
@@ -610,13 +610,13 @@
         <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2672</v>
+        <v>-0.3819</v>
       </c>
       <c r="T2" t="n">
-        <v>0.803</v>
+        <v>0.263</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.6449</v>
       </c>
       <c r="V2" t="n">
         <v>0.7075</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8392</v>
+        <v>3.4562</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06560000000000001</v>
+        <v>1.7981</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9048</v>
+        <v>1.6581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9297</v>
+        <v>2.8644</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4136</v>
+        <v>0.4103</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5161</v>
+        <v>2.4541</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8706</v>
+        <v>3.7332</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0247</v>
+        <v>0.4449</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8953</v>
+        <v>3.2883</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9409</v>
+        <v>-0.8688</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4383</v>
+        <v>-0.0346</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3792</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>2.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2782</v>
+        <v>-0.3306</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5317</v>
+        <v>0.053</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8098</v>
+        <v>-0.3835</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8254</v>
+        <v>-0.0478</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>-0.0478</v>
       </c>
       <c r="X3" t="n">
-        <v>1.3194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3501</v>
+        <v>3.3757</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6374</v>
+        <v>0.016</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7126</v>
+        <v>3.3597</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8644</v>
+        <v>0.9297</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4103</v>
+        <v>0.4136</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4541</v>
+        <v>0.5161</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7332</v>
+        <v>1.8706</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4449</v>
+        <v>-0.0247</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2883</v>
+        <v>1.8953</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8688</v>
+        <v>-0.9409</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0346</v>
+        <v>0.4383</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.3792</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9105</v>
+        <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4367</v>
+        <v>-0.1853</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1077</v>
+        <v>-0.4501</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.329</v>
+        <v>0.2647</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0478</v>
+        <v>2.8254</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0478</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.3194</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9534</v>
+        <v>1.8932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4662</v>
+        <v>2.188</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5128</v>
+        <v>-0.2948</v>
       </c>
       <c r="G5" t="n">
         <v>-2.5276</v>
@@ -844,13 +844,13 @@
         <v>2.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4428</v>
+        <v>-0.503</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9074</v>
+        <v>-0.1857</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5354</v>
+        <v>-0.3174</v>
       </c>
       <c r="V5" t="n">
         <v>3.9537</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0925</v>
+        <v>0.1531</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8478</v>
+        <v>-0.7872</v>
       </c>
       <c r="F6" t="n">
         <v>0.9403</v>
@@ -922,10 +922,10 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>-0</v>
+        <v>0.0606</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3028</v>
+        <v>-0.2423</v>
       </c>
       <c r="U6" t="n">
         <v>0.3028</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>M. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0876</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0589</v>
+        <v>-2.3685</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1465</v>
+        <v>1.8045</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1648</v>
+        <v>-0.4728</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5307</v>
+        <v>0.2356</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3659</v>
+        <v>-0.7085</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3777</v>
+        <v>-1.329</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2719</v>
+        <v>0.0412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6495</v>
+        <v>-1.3702</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5425</v>
+        <v>0.8562</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2589</v>
+        <v>0.1944</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2836</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.825</v>
+        <v>0.1029</v>
       </c>
       <c r="T7" t="n">
-        <v>0.729</v>
+        <v>-0.0693</v>
       </c>
       <c r="U7" t="n">
-        <v>0.096</v>
+        <v>0.1722</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SANCHEZ SANCHEZ</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.976</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5897</v>
+        <v>0.5584</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6137</v>
+        <v>-1.201</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4728</v>
+        <v>-1.1648</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2356</v>
+        <v>-1.5307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7085</v>
+        <v>0.3659</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.329</v>
+        <v>0.3777</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0412</v>
+        <v>-0.2719</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3702</v>
+        <v>0.6495</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8562</v>
+        <v>-1.5425</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1944</v>
+        <v>-1.2589</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.2836</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3091</v>
+        <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2905</v>
+        <v>0.2285</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0186</v>
+        <v>0.0415</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.006</v>
+        <v>-1.6717</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.259</v>
+        <v>-1.4995</v>
       </c>
       <c r="F9" t="n">
-        <v>0.253</v>
+        <v>-0.1722</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.675</v>
+        <v>-0.9663</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2294</v>
+        <v>-0.061</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5544</v>
+        <v>-0.9053</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0436</v>
+        <v>-0.3759</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9278</v>
+        <v>-0.3048</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9715</v>
+        <v>-0.0711</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7187</v>
+        <v>-0.5904</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3015</v>
+        <v>0.2439</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4171</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0675</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6079</v>
+        <v>-0.1534</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4596</v>
+        <v>-0.4923</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8462</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8462</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4371</v>
+        <v>-2.0217</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2193</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.857</v>
+        <v>-1.8025</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0674</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0363</v>
+        <v>0.4517</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.12</v>
+        <v>0.2408</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1564</v>
+        <v>0.2109</v>
       </c>
       <c r="V10" t="n">
         <v>0.5642</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5659</v>
+        <v>-2.4778</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1211</v>
+        <v>-1.3309</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4448</v>
+        <v>-1.1469</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9663</v>
+        <v>-0.0408</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.061</v>
+        <v>0.1038</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9053</v>
+        <v>-0.1446</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3759</v>
+        <v>0.3213</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3048</v>
+        <v>0.3213</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0711</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5904</v>
+        <v>-0.3621</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2439</v>
+        <v>-0.2175</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.1446</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1642</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5399</v>
+        <v>-0.2728</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.775</v>
+        <v>-0.3239</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7649</v>
+        <v>0.051</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2239</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8293</v>
+        <v>-2.6095</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4916</v>
+        <v>-2.6989</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3377</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0408</v>
+        <v>-0.675</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1038</v>
+        <v>-2.2294</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1446</v>
+        <v>1.5544</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3213</v>
+        <v>0.0436</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3213</v>
+        <v>-1.9278</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.9715</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3621</v>
+        <v>-0.7187</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2175</v>
+        <v>-0.3015</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1446</v>
+        <v>-0.4171</v>
       </c>
       <c r="P12" t="n">
         <v>-1.5523</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6243</v>
+        <v>0.464</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4845</v>
+        <v>0.1679</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1397</v>
+        <v>0.2961</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6119</v>
+        <v>-0.8462</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="13">
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.658300000000001</v>
+        <v>2.566800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.500699999999999</v>
+        <v>-2.5921</v>
       </c>
       <c r="F13" t="n">
-        <v>5.158900000000001</v>
+        <v>5.1588</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.364300000000001</v>
+        <v>-4.3643</v>
       </c>
       <c r="H13" t="n">
         <v>-3.6415</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7229000000000001</v>
+        <v>-0.7229000000000003</v>
       </c>
       <c r="J13" t="n">
         <v>5.3557</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4614999999999999</v>
+        <v>0.4615</v>
       </c>
       <c r="L13" t="n">
         <v>4.8942</v>
@@ -1459,7 +1459,7 @@
         <v>-5.616999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>2.910499999999999</v>
+        <v>2.910500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.5226</v>
@@ -1468,13 +1468,13 @@
         <v>18.4331</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8786</v>
+        <v>-0.9701</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3797</v>
+        <v>-0.4715</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4988000000000001</v>
+        <v>-0.4989</v>
       </c>
       <c r="V13" t="n">
         <v>4.991099999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.5181</v>
+        <v>6.981</v>
       </c>
       <c r="E14" t="n">
-        <v>8.4968</v>
+        <v>7.3957</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0213</v>
+        <v>-0.4148</v>
       </c>
       <c r="G14" t="n">
         <v>6.8809</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2194</v>
+        <v>0.6822</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1058</v>
+        <v>0.0047</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1135</v>
+        <v>0.6775</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8696</v>
+        <v>3.488</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2374</v>
+        <v>3.6378</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3678</v>
+        <v>-0.1498</v>
       </c>
       <c r="G15" t="n">
         <v>1.4138</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2427</v>
+        <v>0.3757</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2165</v>
+        <v>0.1839</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0262</v>
+        <v>0.1918</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0478</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7724</v>
+        <v>0.5251</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9608</v>
+        <v>-2.3133</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1884</v>
+        <v>2.8384</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5119</v>
+        <v>-0.4086</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2813</v>
+        <v>0.0091</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2306</v>
+        <v>-0.4176</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5425</v>
+        <v>-1.8596</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6899</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8525</v>
+        <v>-1.2129</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0305</v>
+        <v>1.451</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4087</v>
+        <v>0.6558</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3781</v>
+        <v>0.7952</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9403</v>
+        <v>0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0747</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0366</v>
+        <v>0.8277</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2691</v>
+        <v>0.5165</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7674</v>
+        <v>0.3113</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8358</v>
+        <v>-0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2245</v>
+        <v>0.427</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0606</v>
+        <v>0.8607</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2851</v>
+        <v>-0.4337</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4004</v>
+        <v>3.5119</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1335</v>
+        <v>2.2813</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2669</v>
+        <v>1.2306</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.5425</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.6899</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.8525</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4004</v>
+        <v>-0.0305</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1335</v>
+        <v>-0.4087</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2669</v>
+        <v>0.3781</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-4.0747</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1759</v>
+        <v>0.6912</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0606</v>
+        <v>0.169</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1153</v>
+        <v>0.5221</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1642</v>
+        <v>0.3716</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5135</v>
+        <v>0.9691</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6777</v>
+        <v>-0.5975</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4086</v>
+        <v>-0.4372</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0091</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4176</v>
+        <v>-0.5344</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8596</v>
+        <v>0.5272</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.173</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2129</v>
+        <v>0.7002</v>
       </c>
       <c r="M18" t="n">
-        <v>1.451</v>
+        <v>-0.9644</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6558</v>
+        <v>0.2702</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7952</v>
+        <v>-1.2346</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>2.7164</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4668</v>
+        <v>-0.3062</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3163</v>
+        <v>-0.4044</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1505</v>
+        <v>0.0982</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2821</v>
+        <v>-1.6015</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.2518</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0814</v>
+        <v>-0.0606</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1476</v>
+        <v>0.3124</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.753</v>
+        <v>0.4004</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2257</v>
+        <v>0.1335</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5272</v>
+        <v>0.2669</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1805</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3429</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4275</v>
+        <v>0.4004</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1172</v>
+        <v>0.1335</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6896</v>
+        <v>0.2669</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2669</v>
+        <v>-0.1486</v>
       </c>
       <c r="T19" t="n">
-        <v>0.729</v>
+        <v>-0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5379</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0439</v>
+        <v>-0.5917</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7689</v>
+        <v>-2.682</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8128</v>
+        <v>2.0903</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4372</v>
+        <v>-0.753</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.2257</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5344</v>
+        <v>-0.5272</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5272</v>
+        <v>-1.1805</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.173</v>
+        <v>-1.3429</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7002</v>
+        <v>0.1624</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9644</v>
+        <v>0.4275</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2702</v>
+        <v>1.1172</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2346</v>
+        <v>-0.6896</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7164</v>
+        <v>0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7216</v>
+        <v>0.609</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6046</v>
+        <v>0.1284</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1171</v>
+        <v>0.4806</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6015</v>
+        <v>-1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8462</v>
+        <v>-0.6597</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4477</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9142</v>
+        <v>-0.7323</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1393</v>
+        <v>-0.0392</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7749</v>
+        <v>-0.6932</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4595</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2607</v>
+        <v>-0.0788</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0482</v>
+        <v>0.0519</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0046</v>
+        <v>-3.7076</v>
       </c>
       <c r="E23" t="n">
         <v>-3.0308</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9737</v>
+        <v>-0.6767</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2235</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1332</v>
+        <v>0.1637</v>
       </c>
       <c r="T23" t="n">
         <v>0.5585</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6918</v>
+        <v>-0.3948</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7075</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.023999999999999</v>
+        <v>-6.7171</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.5407</v>
+        <v>-9.639799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5167</v>
+        <v>2.9227</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7169</v>
@@ -2326,13 +2326,13 @@
         <v>2.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.504</v>
+        <v>-0.1971</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2472</v>
+        <v>-0.3463</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2568</v>
+        <v>0.1492</v>
       </c>
       <c r="V24" t="n">
         <v>1.2716</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.658499999999998</v>
+        <v>-0.9909999999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.159</v>
+        <v>-5.158999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5006</v>
+        <v>4.167899999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>4.364499999999999</v>
+        <v>4.3645</v>
       </c>
       <c r="H25" t="n">
-        <v>3.641600000000001</v>
+        <v>3.6416</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7231000000000003</v>
+        <v>0.7230999999999994</v>
       </c>
       <c r="J25" t="n">
         <v>9.720200000000002</v>
@@ -2383,19 +2383,19 @@
         <v>4.102900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>5.6171</v>
+        <v>5.617099999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-5.3556</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4614999999999996</v>
+        <v>-0.4614999999999998</v>
       </c>
       <c r="O25" t="n">
         <v>-4.8941</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.910499999999999</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.4332</v>
@@ -2404,13 +2404,13 @@
         <v>15.5226</v>
       </c>
       <c r="S25" t="n">
-        <v>1.878699999999999</v>
+        <v>2.5459</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4987999999999999</v>
+        <v>0.4988</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3796</v>
+        <v>2.0471</v>
       </c>
       <c r="V25" t="n">
         <v>-4.9912</v>
